--- a/evaluation/bertscore/evaluation_bertscore_table.xlsx
+++ b/evaluation/bertscore/evaluation_bertscore_table.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
   <si>
     <t>No</t>
   </si>
@@ -34,142 +34,136 @@
     <t>Rata-rata</t>
   </si>
   <si>
-    <t>79.39%</t>
-  </si>
-  <si>
-    <t>79.08%</t>
+    <t>79.80%</t>
+  </si>
+  <si>
+    <t>80.11%</t>
   </si>
   <si>
     <t>100.00%</t>
   </si>
   <si>
-    <t>63.97%</t>
-  </si>
-  <si>
-    <t>64.13%</t>
-  </si>
-  <si>
-    <t>62.37%</t>
-  </si>
-  <si>
-    <t>82.06%</t>
-  </si>
-  <si>
-    <t>80.01%</t>
-  </si>
-  <si>
-    <t>64.65%</t>
-  </si>
-  <si>
-    <t>85.18%</t>
-  </si>
-  <si>
-    <t>56.38%</t>
-  </si>
-  <si>
-    <t>65.18%</t>
-  </si>
-  <si>
-    <t>66.96%</t>
-  </si>
-  <si>
-    <t>55.75%</t>
-  </si>
-  <si>
-    <t>65.10%</t>
-  </si>
-  <si>
-    <t>71.35%</t>
-  </si>
-  <si>
-    <t>89.90%</t>
-  </si>
-  <si>
-    <t>88.85%</t>
-  </si>
-  <si>
-    <t>71.58%</t>
-  </si>
-  <si>
-    <t>69.46%</t>
-  </si>
-  <si>
-    <t>68.15%</t>
-  </si>
-  <si>
-    <t>88.45%</t>
-  </si>
-  <si>
-    <t>88.00%</t>
-  </si>
-  <si>
-    <t>58.87%</t>
-  </si>
-  <si>
-    <t>93.34%</t>
-  </si>
-  <si>
-    <t>65.96%</t>
-  </si>
-  <si>
-    <t>68.72%</t>
-  </si>
-  <si>
-    <t>72.19%</t>
-  </si>
-  <si>
-    <t>66.89%</t>
-  </si>
-  <si>
-    <t>72.11%</t>
-  </si>
-  <si>
-    <t>77.50%</t>
-  </si>
-  <si>
-    <t>84.32%</t>
-  </si>
-  <si>
-    <t>83.68%</t>
-  </si>
-  <si>
-    <t>67.56%</t>
-  </si>
-  <si>
-    <t>66.69%</t>
-  </si>
-  <si>
-    <t>65.13%</t>
-  </si>
-  <si>
-    <t>85.14%</t>
-  </si>
-  <si>
-    <t>83.82%</t>
-  </si>
-  <si>
-    <t>61.63%</t>
-  </si>
-  <si>
-    <t>89.08%</t>
-  </si>
-  <si>
-    <t>60.80%</t>
-  </si>
-  <si>
-    <t>66.90%</t>
-  </si>
-  <si>
-    <t>69.48%</t>
-  </si>
-  <si>
-    <t>60.82%</t>
-  </si>
-  <si>
-    <t>68.43%</t>
-  </si>
-  <si>
-    <t>74.23%</t>
+    <t>80.38%</t>
+  </si>
+  <si>
+    <t>85.30%</t>
+  </si>
+  <si>
+    <t>88.20%</t>
+  </si>
+  <si>
+    <t>87.94%</t>
+  </si>
+  <si>
+    <t>87.24%</t>
+  </si>
+  <si>
+    <t>89.79%</t>
+  </si>
+  <si>
+    <t>91.57%</t>
+  </si>
+  <si>
+    <t>83.99%</t>
+  </si>
+  <si>
+    <t>77.66%</t>
+  </si>
+  <si>
+    <t>82.56%</t>
+  </si>
+  <si>
+    <t>90.59%</t>
+  </si>
+  <si>
+    <t>84.35%</t>
+  </si>
+  <si>
+    <t>85.97%</t>
+  </si>
+  <si>
+    <t>93.66%</t>
+  </si>
+  <si>
+    <t>93.77%</t>
+  </si>
+  <si>
+    <t>96.79%</t>
+  </si>
+  <si>
+    <t>95.00%</t>
+  </si>
+  <si>
+    <t>97.38%</t>
+  </si>
+  <si>
+    <t>97.11%</t>
+  </si>
+  <si>
+    <t>97.87%</t>
+  </si>
+  <si>
+    <t>97.00%</t>
+  </si>
+  <si>
+    <t>95.20%</t>
+  </si>
+  <si>
+    <t>93.23%</t>
+  </si>
+  <si>
+    <t>95.73%</t>
+  </si>
+  <si>
+    <t>98.40%</t>
+  </si>
+  <si>
+    <t>93.47%</t>
+  </si>
+  <si>
+    <t>96.13%</t>
+  </si>
+  <si>
+    <t>86.18%</t>
+  </si>
+  <si>
+    <t>86.40%</t>
+  </si>
+  <si>
+    <t>87.82%</t>
+  </si>
+  <si>
+    <t>89.89%</t>
+  </si>
+  <si>
+    <t>92.56%</t>
+  </si>
+  <si>
+    <t>92.42%</t>
+  </si>
+  <si>
+    <t>91.92%</t>
+  </si>
+  <si>
+    <t>94.21%</t>
+  </si>
+  <si>
+    <t>89.24%</t>
+  </si>
+  <si>
+    <t>84.73%</t>
+  </si>
+  <si>
+    <t>88.66%</t>
+  </si>
+  <si>
+    <t>94.33%</t>
+  </si>
+  <si>
+    <t>88.67%</t>
+  </si>
+  <si>
+    <t>90.71%</t>
   </si>
 </sst>
 </file>
@@ -558,10 +552,10 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -575,10 +569,10 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -609,10 +603,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -626,10 +620,10 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -643,10 +637,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -657,13 +651,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -674,13 +668,13 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -691,13 +685,13 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -708,13 +702,13 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -725,13 +719,13 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -742,13 +736,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -759,13 +753,13 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -776,13 +770,13 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -793,13 +787,13 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -810,13 +804,13 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
